--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-logical-model.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-logical-model.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T01:04:27+00:00</t>
+    <t>2026-10-19T02:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -424,7 +424,7 @@
 </t>
   </si>
   <si>
-    <t>Report interpreter</t>
+    <t>Results interpreter</t>
   </si>
   <si>
     <t>Person who clinically assesses and is responsible for the report.</t>
@@ -437,10 +437,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen material</t>
-  </si>
-  <si>
-    <t>Specimen materials on which the report is based.</t>
+    <t>Specimen</t>
+  </si>
+  <si>
+    <t>Specimens on which the report is based.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-logical-model-de.Untersuchung</t>

--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-logical-model.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-logical-model.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T02:33:36+00:00</t>
+    <t>2026-10-19T02:49:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
